--- a/data/trans_dic/P62-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,57; 81,94</t>
+          <t>75,56; 82,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,37; 73,23</t>
+          <t>66,47; 73,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,01; 75,93</t>
+          <t>68,9; 76,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,1; 81,75</t>
+          <t>73,97; 81,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,08; 41,85</t>
+          <t>35,89; 41,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,64; 48,25</t>
+          <t>42,64; 48,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,75; 50,31</t>
+          <t>43,66; 50,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,94; 59,58</t>
+          <t>53,77; 59,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,7; 55,57</t>
+          <t>50,8; 55,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,95; 57,43</t>
+          <t>52,98; 57,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,72; 59,88</t>
+          <t>54,55; 59,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,88; 66,5</t>
+          <t>61,9; 66,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,0; 33,91</t>
+          <t>26,72; 34,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,95; 29,79</t>
+          <t>23,83; 29,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 37,2</t>
+          <t>31,35; 37,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,43; 47,22</t>
+          <t>39,6; 47,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 10,45</t>
+          <t>6,88; 10,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,09</t>
+          <t>12,43; 17,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 22,24</t>
+          <t>17,71; 22,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,52; 61,54</t>
+          <t>25,49; 62,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 18,27</t>
+          <t>14,41; 18,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 22,17</t>
+          <t>18,44; 22,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 28,46</t>
+          <t>24,81; 28,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,33; 56,01</t>
+          <t>33,26; 57,56</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,94; 50,68</t>
+          <t>34,19; 51,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 36,88</t>
+          <t>21,06; 36,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,54; 43,86</t>
+          <t>28,93; 43,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,86; 64,21</t>
+          <t>49,2; 63,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,0; 28,78</t>
+          <t>16,91; 28,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,27; 22,21</t>
+          <t>11,66; 22,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,6; 28,72</t>
+          <t>17,13; 28,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,15; 39,75</t>
+          <t>29,13; 39,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,12; 36,17</t>
+          <t>25,97; 36,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 26,25</t>
+          <t>16,75; 25,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 33,4</t>
+          <t>24,05; 33,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,02; 48,98</t>
+          <t>40,38; 48,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,84; 57,23</t>
+          <t>51,94; 57,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,93; 46,39</t>
+          <t>41,78; 46,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,17; 48,68</t>
+          <t>44,21; 48,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,96; 57,01</t>
+          <t>51,09; 57,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 26,4</t>
+          <t>22,96; 26,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,34; 30,91</t>
+          <t>27,23; 30,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,28; 32,24</t>
+          <t>28,35; 32,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>37,06; 57,99</t>
+          <t>36,85; 58,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,06; 37,23</t>
+          <t>34,13; 37,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,9; 36,99</t>
+          <t>34,11; 37,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,76; 38,8</t>
+          <t>35,92; 38,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,04; 56,13</t>
+          <t>43,91; 57,43</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que percibe algun tipo de pensión</t>
+          <t>Población que percibe algun tipo de pensión (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>491030; 532390</t>
+          <t>490935; 532822</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>521423; 575298</t>
+          <t>522223; 574656</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>419465; 461561</t>
+          <t>418814; 462837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>282881; 312071</t>
+          <t>282366; 312502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>418763; 485756</t>
+          <t>416619; 482700</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>505061; 571528</t>
+          <t>505027; 571164</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>398173; 457868</t>
+          <t>397312; 460845</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>361068; 398809</t>
+          <t>359902; 396364</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>917858; 1006017</t>
+          <t>919681; 1001885</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1043092; 1131355</t>
+          <t>1043796; 1135324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>830582; 908984</t>
+          <t>828083; 910058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>650372; 698984</t>
+          <t>650652; 702236</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146854; 191524</t>
+          <t>150923; 192230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>246923; 307067</t>
+          <t>245711; 306420</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>355482; 421168</t>
+          <t>354867; 421760</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>355925; 426274</t>
+          <t>357495; 430005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69065; 104567</t>
+          <t>68881; 105843</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147596; 199004</t>
+          <t>144719; 197907</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>226296; 289897</t>
+          <t>230826; 292103</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>328186; 791371</t>
+          <t>327835; 803389</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>230433; 285988</t>
+          <t>225570; 284655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>407127; 486607</t>
+          <t>404749; 484284</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>604921; 693269</t>
+          <t>604332; 693357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>729528; 1225830</t>
+          <t>728001; 1259746</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49121; 73345</t>
+          <t>49482; 73913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34259; 59672</t>
+          <t>34071; 59594</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57019; 84659</t>
+          <t>55841; 83818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94490; 124175</t>
+          <t>95160; 122050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29610; 53262</t>
+          <t>31284; 53624</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24988; 49238</t>
+          <t>25856; 49526</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39388; 68130</t>
+          <t>40640; 67157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63146; 86099</t>
+          <t>63090; 85874</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>86133; 119271</t>
+          <t>85628; 121459</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66756; 100665</t>
+          <t>64217; 99044</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102101; 143683</t>
+          <t>103493; 142735</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>164083; 200824</t>
+          <t>165554; 200090</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>704703; 777999</t>
+          <t>706023; 776905</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>829532; 917731</t>
+          <t>826521; 915197</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>853779; 941046</t>
+          <t>854515; 945374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>753042; 842535</t>
+          <t>755077; 843575</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>535011; 619576</t>
+          <t>538793; 620420</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>702840; 794601</t>
+          <t>700022; 792427</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>692959; 790172</t>
+          <t>694886; 789375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>804830; 1259545</t>
+          <t>800311; 1275030</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1262052; 1379693</t>
+          <t>1264825; 1381379</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1541801; 1682470</t>
+          <t>1551756; 1691525</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1567843; 1700884</t>
+          <t>1574572; 1707814</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1607452; 2048576</t>
+          <t>1602702; 2096065</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P62-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,56; 82,0</t>
+          <t>75,46; 81,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,47; 73,15</t>
+          <t>66,55; 73,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,9; 76,14</t>
+          <t>68,74; 76,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,97; 81,86</t>
+          <t>73,19; 80,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,89; 41,59</t>
+          <t>36,12; 41,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,64; 48,22</t>
+          <t>42,59; 48,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,66; 50,64</t>
+          <t>43,33; 50,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>53,77; 59,22</t>
+          <t>53,76; 59,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,8; 55,34</t>
+          <t>50,71; 55,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,98; 57,63</t>
+          <t>53,05; 57,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,55; 59,95</t>
+          <t>54,67; 59,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>61,9; 66,81</t>
+          <t>61,61; 66,41</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,72; 34,03</t>
+          <t>26,36; 34,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 29,72</t>
+          <t>23,88; 29,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,35; 37,25</t>
+          <t>31,4; 37,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,6; 47,64</t>
+          <t>41,47; 48,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,58</t>
+          <t>7,0; 10,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 17,0</t>
+          <t>12,67; 17,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,71; 22,41</t>
+          <t>17,4; 22,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,49; 62,48</t>
+          <t>23,25; 27,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 18,18</t>
+          <t>14,52; 18,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,44; 22,06</t>
+          <t>18,59; 22,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 28,47</t>
+          <t>25,01; 28,66</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,26; 57,56</t>
+          <t>32,09; 36,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,19; 51,08</t>
+          <t>33,72; 50,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,06; 36,83</t>
+          <t>20,05; 36,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,93; 43,42</t>
+          <t>28,72; 43,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,2; 63,11</t>
+          <t>48,53; 63,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,91; 28,98</t>
+          <t>16,79; 29,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 22,34</t>
+          <t>11,51; 22,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 28,31</t>
+          <t>16,62; 28,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,13; 39,64</t>
+          <t>29,61; 40,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,97; 36,83</t>
+          <t>25,96; 36,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,75; 25,83</t>
+          <t>16,94; 26,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,05; 33,17</t>
+          <t>24,11; 33,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,38; 48,8</t>
+          <t>40,55; 49,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,94; 57,15</t>
+          <t>51,86; 57,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,78; 46,26</t>
+          <t>41,81; 46,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,21; 48,91</t>
+          <t>44,03; 48,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,09; 57,08</t>
+          <t>52,39; 57,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,96; 26,44</t>
+          <t>22,86; 26,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,23; 30,83</t>
+          <t>27,27; 30,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,35; 32,21</t>
+          <t>28,33; 32,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,85; 58,71</t>
+          <t>34,96; 38,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,13; 37,28</t>
+          <t>34,19; 37,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,11; 37,19</t>
+          <t>34,0; 36,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,92; 38,96</t>
+          <t>35,95; 38,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,91; 57,43</t>
+          <t>43,0; 45,87</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>298869</t>
+          <t>320791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>378251</t>
+          <t>411773</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>677120</t>
+          <t>732564</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>490935; 532822</t>
+          <t>490287; 530610</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>522223; 574656</t>
+          <t>522784; 576834</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>418814; 462837</t>
+          <t>417820; 462418</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>282366; 312502</t>
+          <t>302573; 333767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>416619; 482700</t>
+          <t>419289; 483733</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>505027; 571164</t>
+          <t>504414; 572080</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>397312; 460845</t>
+          <t>394343; 459563</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>359902; 396364</t>
+          <t>392100; 433491</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>919681; 1001885</t>
+          <t>918187; 1001650</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1043796; 1135324</t>
+          <t>1045123; 1132304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>828083; 910058</t>
+          <t>829902; 904334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>650652; 702236</t>
+          <t>703973; 758906</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392185</t>
+          <t>427767</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>488387</t>
+          <t>310825</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>880573</t>
+          <t>738592</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>150923; 192230</t>
+          <t>148913; 192822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>245711; 306420</t>
+          <t>246187; 304025</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>354867; 421760</t>
+          <t>355496; 419388</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>357495; 430005</t>
+          <t>394666; 462250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68881; 105843</t>
+          <t>70056; 107380</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>144719; 197907</t>
+          <t>147497; 198460</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>230826; 292103</t>
+          <t>226871; 287288</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>327835; 803389</t>
+          <t>283354; 337744</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>225570; 284655</t>
+          <t>227301; 288736</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>404749; 484284</t>
+          <t>408039; 493081</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>604332; 693357</t>
+          <t>609231; 698061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>728001; 1259746</t>
+          <t>696531; 781515</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108345</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73973</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>182318</t>
+          <t>208644</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>49482; 73913</t>
+          <t>48792; 72708</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34071; 59594</t>
+          <t>32431; 58346</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55841; 83818</t>
+          <t>55444; 83670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95160; 122050</t>
+          <t>105396; 137765</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31284; 53624</t>
+          <t>31069; 53894</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25856; 49526</t>
+          <t>25520; 48910</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40640; 67157</t>
+          <t>39438; 68310</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63090; 85874</t>
+          <t>73413; 99310</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85628; 121459</t>
+          <t>85615; 119260</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64217; 99044</t>
+          <t>64973; 100368</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103493; 142735</t>
+          <t>103737; 142971</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>165554; 200090</t>
+          <t>188602; 228567</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>799398</t>
+          <t>871527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>940611</t>
+          <t>808272</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1740010</t>
+          <t>1679800</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>706023; 776905</t>
+          <t>704978; 776480</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>826521; 915197</t>
+          <t>827165; 913772</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>854515; 945374</t>
+          <t>851113; 942934</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>755077; 843575</t>
+          <t>828989; 916455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>538793; 620420</t>
+          <t>536304; 621544</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>700022; 792427</t>
+          <t>700994; 791078</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>694886; 789375</t>
+          <t>694199; 789939</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>800311; 1275030</t>
+          <t>767574; 846083</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1264825; 1381379</t>
+          <t>1267016; 1382544</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1551756; 1691525</t>
+          <t>1546579; 1678586</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1574572; 1707814</t>
+          <t>1575918; 1701106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1602702; 2096065</t>
+          <t>1624681; 1732932</t>
         </is>
       </c>
     </row>
